--- a/data/course_manage.xlsx
+++ b/data/course_manage.xlsx
@@ -157,7 +157,7 @@
     <t>第一节.mp4</t>
   </si>
   <si>
-    <t>https://xxx.mp4</t>
+    <t>https://1327452496.vod-qcloud.com/80aa29cdvodcq1327452496/812f7a0e5001834811100541528/nuiIBCrjsSIA.mp4</t>
   </si>
 </sst>
 </file>
@@ -789,11 +789,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1158,76 +1155,76 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="20" customHeight="1" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="4" width="15" style="4" customWidth="1"/>
-    <col min="5" max="5" width="24.25" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="15" style="4" customWidth="1"/>
+    <col min="1" max="4" width="15" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.25" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="15" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1243,76 +1240,76 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="15.75" defaultRowHeight="19" customHeight="1" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="4" width="15.75" style="4" customWidth="1"/>
-    <col min="5" max="5" width="52.25" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="15.75" style="4" customWidth="1"/>
+    <col min="1" max="4" width="15.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="52.25" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="15.75" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1328,100 +1325,100 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="17" defaultRowHeight="19" customHeight="1" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="17" style="4" customWidth="1"/>
-    <col min="7" max="7" width="46" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="17" style="4" customWidth="1"/>
+    <col min="1" max="6" width="17" style="3" customWidth="1"/>
+    <col min="7" max="7" width="46" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="17" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:7">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:7">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:7">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:7">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1438,12 +1435,12 @@
   <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="19" customHeight="1" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="3" width="11.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="136.5" style="1" customWidth="1"/>
     <col min="5" max="16384" width="11.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1457,7 +1454,7 @@
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:4">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1">
@@ -1466,13 +1463,13 @@
       <c r="C2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://xxx.mp4"/>
+    <hyperlink ref="D2" r:id="rId1" display="https://1327452496.vod-qcloud.com/80aa29cdvodcq1327452496/812f7a0e5001834811100541528/nuiIBCrjsSIA.mp4" tooltip="https://1327452496.vod-qcloud.com/80aa29cdvodcq1327452496/812f7a0e5001834811100541528/nuiIBCrjsSIA.mp4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data/course_manage.xlsx
+++ b/data/course_manage.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="courses" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="126">
   <si>
     <t>course_id</t>
   </si>
@@ -106,42 +106,300 @@
     <t>video_url</t>
   </si>
   <si>
-    <t>认识1-10的认识《数字歌》</t>
-  </si>
-  <si>
-    <t>1第一节.mp4</t>
+    <t xml:space="preserve">	1第一节1-10的认识《数字歌》.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/4115f9ca5001834815917756870/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2第二节：0的认识，加与减.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/15412c085001834815859658241/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	3第三节相邻数.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/42ae2c195001834815887795759/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	4第四节认识大于号、小于号.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/f97736005001834815845816116/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	5第五节认识单双数.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/412547eb5001834815917761596/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	6第六节：2和3的分解与组合.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/5bacc91c5001834815867125124/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	7第7节：4的分解与组合.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/6b46cb455001834815904614876/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	8第八节：5的分解与组合.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/6b46cedf5001834815904614924/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	9第九节：6的分解与组合.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/150707c55001834815859621158/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	10第十节：7的分解与组合.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/1bd633245001834815818845307/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	11第十一节：8的分解与组合.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/5baa10645001834815867120299/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	12第十二节：9的分解与组合.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/f97747425001834815845816532/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	13第十三节：10的分解与组合.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/412547c75001834815917761583/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	14第十四节：6-10以内分解与组合.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/4f98ff175001834815799574859/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	15第十五节：《凑十歌》.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/41264f245001834815917763155/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	16第十六节：10以内加法【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/f977cb255001834815845817336/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	17第十七节：10以内减法【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/5182a4a75001834815799616630/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	18第十八节：10以内减法【速算2】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/f74317265001834815845730991/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	19第十九节：10以内连加连减混合运算.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/2d0a91c65001834815808718347/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	20第二十节：20以内不进位加法【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/f978ec645001834815845819531/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	21第二十一节：20以内不退位减法【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/4f97d12a5001834815799572362/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	22第二十二节：20以内进位加法【凑十法】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/150824c85001834815859623258/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	23第二十三节：20以内进位加法【补数法】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/2b1fbd5e5001834815808674005/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	24第二十四节：20以内退位减法【破十法】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/42af33725001834815887797327/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	25第二十五节：20以内退位减法【平十法】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/4f9979c65001834815799575400/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	26第二十六节：20以内退位减法【补数法】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/1540b02f5001834815859657609/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	27第二十七节：20以内连加连减混合运算.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/2b2056815001834815808675304/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	28第二十八节100以内不进位加法【速算】(两位数加一位数).mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/5be16d7e5001834815867152126/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	29第二十九节100以内不进位加法【速算】(两位数加两位数).mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/1bd41bcc5001834815818841958/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	30第三十节100以内不退位减法【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/518214685001834815799615560/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	31第三十一节100以内进位加法(两位数加一位数).mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/154ee57f5001834815859660320/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	32第三十二节100以内进位加法(两位数加两位数).mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/f98608585001834815845820203/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	33第三十三节100以内退位减法【速算】(两位数减一位数).mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/f977d4055001834815845817561/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	34第三十四节100以内退位减法【速算2】(两位数减一位数).mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/2b1d8bf65001834815808670010/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	35第三十五节100以内退位减法(速算)(两位数减两位数).mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/5183ca935001834815799618964/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	36第三十六节100以内退位减法(速算2)(两位数减两位数).mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/2b1fd3a75001834815808674581/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	37第三十七节百数表1.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/6b46c2df5001834815904614681/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	38第三十八节百数表2.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/445ff0315001834815887804868/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	39第三十九节经典括号题1【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/42af3bef5001834815887797522/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	40第四十节经典括号题2【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/15413d515001834815859658664/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	41第四十一节经典括号题3【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/1508b0c05001834815859624222/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	42第四十二节经典括号题4【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/f734ae3c5001834815845727030/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	43第四十三节经典括号题5【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/519397475001834815799624307/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	44第四十四节经典括号题6【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/5182adf35001834815799616894/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	45第四十五节经典括号题7【速算】.mp4</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/6b46319c5001834815904613535/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	46第四十六节连加连减速算.MOV</t>
+  </si>
+  <si>
+    <t>https://1327452496.vod-qcloud.com/57941775vodtranscq1327452496/1bc5bc8c5001834815818838286/v.f1980292.mp4</t>
+  </si>
+  <si>
+    <t>chapter_id</t>
+  </si>
+  <si>
+    <t>chapter_name</t>
+  </si>
+  <si>
+    <t>二年级</t>
+  </si>
+  <si>
+    <t>凑十法</t>
+  </si>
+  <si>
+    <t>01.mp4</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>0的认识，加与减</t>
-  </si>
-  <si>
-    <t>2第二节.mp4</t>
-  </si>
-  <si>
-    <t>相邻数</t>
-  </si>
-  <si>
-    <t>3第三节.mp4</t>
-  </si>
-  <si>
-    <t>chapter_id</t>
-  </si>
-  <si>
-    <t>chapter_name</t>
-  </si>
-  <si>
-    <t>二年级</t>
-  </si>
-  <si>
-    <t>凑十法</t>
-  </si>
-  <si>
-    <t>01.mp4</t>
-  </si>
-  <si>
     <t>破十法</t>
   </si>
   <si>
@@ -155,9 +413,6 @@
   </si>
   <si>
     <t>第一节.mp4</t>
-  </si>
-  <si>
-    <t>https://1327452496.vod-qcloud.com/80aa29cdvodcq1327452496/812f7a0e5001834811100541528/nuiIBCrjsSIA.mp4</t>
   </si>
 </sst>
 </file>
@@ -170,7 +425,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,7 +442,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -199,9 +454,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -659,142 +920,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -802,6 +1063,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1237,11 +1504,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="15.75" defaultRowHeight="19" customHeight="1" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr defaultColWidth="15.75" defaultRowHeight="19" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="4" width="15.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="52.25" style="3" customWidth="1"/>
+    <col min="1" max="2" width="15.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="61.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="68.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="151.783333333333" style="3" customWidth="1"/>
     <col min="6" max="16384" width="15.75" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1269,14 +1538,14 @@
       <c r="B2" s="3">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
@@ -1286,14 +1555,14 @@
       <c r="B3" s="3">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
@@ -1303,14 +1572,745 @@
       <c r="B4" s="3">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="5" customHeight="1" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="D5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3">
+        <v>7</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3">
+        <v>11</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3">
+        <v>13</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="3">
+        <v>14</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="3">
+        <v>15</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="3">
+        <v>16</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="3">
+        <v>17</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="3">
+        <v>18</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="3">
+        <v>19</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="3">
+        <v>20</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="3">
+        <v>21</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="3">
+        <v>22</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="3">
+        <v>23</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="3">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="3">
         <v>25</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="3">
+        <v>26</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="3">
+        <v>27</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3">
+        <v>28</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="3">
+        <v>29</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="3">
+        <v>30</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="3">
+        <v>31</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3">
+        <v>32</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="3">
+        <v>33</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="3">
+        <v>34</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="3">
+        <v>35</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="3">
+        <v>36</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="3">
+        <v>37</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="3">
+        <v>38</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="3">
+        <v>39</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="3">
+        <v>40</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="3">
+        <v>41</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="3">
+        <v>42</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="3">
+        <v>43</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="3">
+        <v>44</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="3">
+        <v>45</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="3">
+        <v>46</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1335,10 +2335,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>19</v>
@@ -1361,19 +2361,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:7">
@@ -1384,19 +2384,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:7">
@@ -1407,19 +2407,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1454,23 +2454,18 @@
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:4">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="D2" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://1327452496.vod-qcloud.com/80aa29cdvodcq1327452496/812f7a0e5001834811100541528/nuiIBCrjsSIA.mp4" tooltip="https://1327452496.vod-qcloud.com/80aa29cdvodcq1327452496/812f7a0e5001834811100541528/nuiIBCrjsSIA.mp4"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/data/course_manage.xlsx
+++ b/data/course_manage.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="courses" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="125">
   <si>
     <t>course_id</t>
   </si>
@@ -410,9 +410,6 @@
   </si>
   <si>
     <t>多位数计算</t>
-  </si>
-  <si>
-    <t>第一节.mp4</t>
   </si>
 </sst>
 </file>
@@ -440,12 +437,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -454,15 +449,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -920,12 +917,12 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1050,25 +1047,22 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1422,76 +1416,76 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="20" customHeight="1" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="4" width="15" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.25" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="15" style="3" customWidth="1"/>
+    <col min="1" max="4" width="15" style="4" customWidth="1"/>
+    <col min="5" max="5" width="24.25" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="15" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:5">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1507,809 +1501,809 @@
   <dimension ref="A1:E47"/>
   <sheetFormatPr defaultColWidth="15.75" defaultRowHeight="19" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" width="15.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="61.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="68.375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="151.783333333333" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="15.75" style="3" customWidth="1"/>
+    <col min="1" max="2" width="15.75" style="4" customWidth="1"/>
+    <col min="3" max="3" width="61.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="68.375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="151.783333333333" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="15.75" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:5">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:5">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:5">
-      <c r="A6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3">
-        <v>5</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:5">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3">
+      <c r="A7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:5">
-      <c r="A8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="A8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4">
         <v>7</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:5">
-      <c r="A9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3">
+      <c r="A9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4">
         <v>8</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:5">
-      <c r="A10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4">
         <v>9</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:5">
-      <c r="A11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="3">
+      <c r="A11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4">
         <v>10</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:5">
-      <c r="A12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="3">
+      <c r="A12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="4">
         <v>11</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:5">
-      <c r="A13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="3">
+      <c r="A13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="4">
         <v>12</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:5">
-      <c r="A14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="A14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="4">
         <v>13</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:5">
-      <c r="A15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="3">
+      <c r="A15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="4">
         <v>14</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:5">
-      <c r="A16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="3">
+      <c r="A16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="4">
         <v>15</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="3">
+      <c r="A17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="4">
         <v>16</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="3">
+      <c r="A18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="4">
         <v>17</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="3">
+      <c r="A19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="4">
         <v>18</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="3">
+      <c r="A20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="4">
         <v>19</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="3">
+      <c r="A21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="4">
         <v>20</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="A22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="4">
         <v>21</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="3">
+      <c r="A23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="4">
         <v>22</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="3">
+      <c r="A24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="4">
         <v>23</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="3">
+      <c r="A25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="4">
         <v>24</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="3">
+      <c r="A26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="4">
         <v>25</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="3">
+      <c r="A27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="4">
         <v>26</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="3">
+      <c r="A28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="4">
         <v>27</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="3">
+      <c r="A29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="4">
         <v>28</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="3">
+      <c r="A30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="4">
         <v>29</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" s="3">
+      <c r="A31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="4">
         <v>30</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" s="3">
+      <c r="A32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="4">
         <v>31</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="3">
+      <c r="A33" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="4">
         <v>32</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="3" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" s="3">
+      <c r="A34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="4">
         <v>33</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="3" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="3">
+      <c r="A35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="4">
         <v>34</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="3">
+      <c r="A36" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="4">
         <v>35</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="3" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" s="3">
+      <c r="A37" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="4">
         <v>36</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="3" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" s="3">
+      <c r="A38" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="4">
         <v>37</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" s="3">
+      <c r="A39" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="4">
         <v>38</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="3" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" s="3">
+      <c r="A40" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="4">
         <v>39</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="3" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B41" s="3">
+      <c r="A41" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="4">
         <v>40</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="3" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B42" s="3">
+      <c r="A42" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="4">
         <v>41</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" s="3">
+      <c r="A43" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="4">
         <v>42</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44" s="3">
+      <c r="A44" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="4">
         <v>43</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="3" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" s="3">
+      <c r="A45" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="4">
         <v>44</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="3" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B46" s="3">
+      <c r="A46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="4">
         <v>45</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="3" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="3">
+      <c r="A47" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="4">
         <v>46</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="3" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2325,100 +2319,100 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="17" defaultRowHeight="19" customHeight="1" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="17" style="3" customWidth="1"/>
-    <col min="7" max="7" width="46" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="17" style="3" customWidth="1"/>
+    <col min="1" max="6" width="17" style="4" customWidth="1"/>
+    <col min="7" max="7" width="46" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="17" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:7">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2431,10 +2425,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="19" customHeight="1" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="19" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="3" width="11.25" style="1" customWidth="1"/>
+    <col min="1" max="2" width="11.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="60.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="136.5" style="1" customWidth="1"/>
     <col min="5" max="16384" width="11.25" style="1" customWidth="1"/>
   </cols>
@@ -2454,16 +2449,648 @@
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:4">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:4">
+      <c r="A3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:4">
+      <c r="A4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:4">
+      <c r="A5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:4">
+      <c r="A6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:4">
+      <c r="A7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:4">
+      <c r="A8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:4">
+      <c r="A9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:4">
+      <c r="A10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:4">
+      <c r="A11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:4">
+      <c r="A12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:4">
+      <c r="A13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:4">
+      <c r="A14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:4">
+      <c r="A15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:4">
+      <c r="A16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:4">
+      <c r="A17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:4">
+      <c r="A18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:4">
+      <c r="A19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:4">
+      <c r="A20" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:4">
+      <c r="A21" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:4">
+      <c r="A22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="1">
+        <v>21</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:4">
+      <c r="A23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="1">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:4">
+      <c r="A24" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="1">
+        <v>23</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:4">
+      <c r="A25" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="1">
+        <v>24</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:4">
+      <c r="A26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="1">
+        <v>25</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:4">
+      <c r="A27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="1">
+        <v>26</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:4">
+      <c r="A28" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="1">
+        <v>27</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:4">
+      <c r="A29" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="1">
+        <v>28</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:4">
+      <c r="A30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="1">
+        <v>29</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:4">
+      <c r="A31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="1">
+        <v>30</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:4">
+      <c r="A32" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="1">
+        <v>31</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:4">
+      <c r="A33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="1">
+        <v>32</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:4">
+      <c r="A34" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="1">
+        <v>33</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:4">
+      <c r="A35" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="1">
+        <v>34</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:4">
+      <c r="A36" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="1">
+        <v>35</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:4">
+      <c r="A37" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="1">
+        <v>36</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:4">
+      <c r="A38" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="1">
+        <v>37</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:4">
+      <c r="A39" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="1">
+        <v>38</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:4">
+      <c r="A40" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="1">
+        <v>39</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:4">
+      <c r="A41" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="1">
+        <v>40</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:4">
+      <c r="A42" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="1">
+        <v>41</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:4">
+      <c r="A43" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="1">
+        <v>42</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:4">
+      <c r="A44" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="1">
+        <v>43</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:4">
+      <c r="A45" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="1">
+        <v>44</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:4">
+      <c r="A46" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="1">
+        <v>45</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:4">
+      <c r="A47" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>114</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
